--- a/docs/TPI_Journal_de_Travail_Anthony.xlsx
+++ b/docs/TPI_Journal_de_Travail_Anthony.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/pv22nbo_eduvaud_ch/Documents/Bureau/TPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1989" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AA00EC0-7832-4853-AC68-B0961F1F0C76}"/>
+  <xr:revisionPtr revIDLastSave="2131" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4649454-165F-4FE0-B30F-EA36E5D9EB9C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$F$85</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$F$106</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="165">
   <si>
     <t>Jour</t>
   </si>
@@ -492,7 +492,52 @@
     <t>en .docx et .xlsx</t>
   </si>
   <si>
-    <t>Mettre la documentation et le JDT dans le dépôt 10:48</t>
+    <t xml:space="preserve">Mettre la documentation et le JDT dans le dépôt </t>
+  </si>
+  <si>
+    <t>Changer le JOIN en INNER JOIN dans   get_teacher_follow_ups()</t>
+  </si>
+  <si>
+    <t>Page admin - Problème avec tracking_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Régler Problème Saisir un suivi    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changement Tableau TOUS LES SUIVIS </t>
+  </si>
+  <si>
+    <t>Quand un admin fait un suivi il n y avait pas marque que c'était l'admin</t>
+  </si>
+  <si>
+    <t>Onglets - SAISIR UN SUIVI ET TOUS LES SUIVIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vérification fonctionnelle pour la page admin </t>
+  </si>
+  <si>
+    <t>Création Feature pour les tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Security.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test unitaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test d'intégration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Documentation  </t>
+  </si>
+  <si>
+    <t>Partie Tests - Test unitaires et Test d'intégration</t>
+  </si>
+  <si>
+    <t>Test Fonctionnels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Fonctionnels </t>
   </si>
 </sst>
 </file>
@@ -1239,13 +1284,13 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.9</c:v>
+                  <c:v>27.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.9</c:v>
+                  <c:v>16.399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>3.5</c:v>
@@ -1254,7 +1299,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5</c:v>
+                  <c:v>5.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1926,7 +1971,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9290911" cy="6045953"/>
+    <xdr:ext cx="9300253" cy="6057472"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1">
@@ -4065,10 +4110,16 @@
       <c r="B93" s="14">
         <v>4</v>
       </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
+      <c r="C93" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F93" s="17"/>
     </row>
     <row r="94" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
@@ -4077,10 +4128,18 @@
       <c r="B94" s="14">
         <v>4</v>
       </c>
-      <c r="C94" s="11"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
+      <c r="C94" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="95" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
@@ -4089,10 +4148,18 @@
       <c r="B95" s="14">
         <v>4</v>
       </c>
-      <c r="C95" s="11"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
+      <c r="C95" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="96" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
@@ -4101,9 +4168,15 @@
       <c r="B96" s="14">
         <v>4</v>
       </c>
-      <c r="C96" s="11"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="8"/>
+      <c r="C96" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="F96" s="8"/>
     </row>
     <row r="97" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4113,10 +4186,18 @@
       <c r="B97" s="14">
         <v>4</v>
       </c>
-      <c r="C97" s="11"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
+      <c r="C97" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="98" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
@@ -4125,73 +4206,167 @@
       <c r="B98" s="14">
         <v>4</v>
       </c>
-      <c r="C98" s="11"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="8"/>
+      <c r="C98" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="F98" s="8"/>
     </row>
     <row r="99" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-      <c r="B99" s="14"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
+      <c r="A99" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B99" s="14">
+        <v>4</v>
+      </c>
+      <c r="C99" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="100" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="6"/>
-      <c r="B100" s="14"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
+      <c r="A100" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B100" s="14">
+        <v>4</v>
+      </c>
+      <c r="C100" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="101" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="14"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="8"/>
+      <c r="A101" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B101" s="14">
+        <v>4</v>
+      </c>
+      <c r="C101" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="F101" s="8"/>
     </row>
     <row r="102" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="14"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
+      <c r="A102" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B102" s="14">
+        <v>4</v>
+      </c>
+      <c r="C102" s="11">
+        <v>2.25</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="14"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="8"/>
+      <c r="A103" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B103" s="14">
+        <v>4</v>
+      </c>
+      <c r="C103" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="F103" s="8"/>
     </row>
     <row r="104" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="14"/>
-      <c r="C104" s="11"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
+      <c r="A104" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B104" s="14">
+        <v>4</v>
+      </c>
+      <c r="C104" s="11">
+        <v>1</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="105" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="14"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="8"/>
+      <c r="A105" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B105" s="14">
+        <v>4</v>
+      </c>
+      <c r="C105" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="F105" s="8"/>
     </row>
     <row r="106" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="14"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="8"/>
+      <c r="A106" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B106" s="14">
+        <v>4</v>
+      </c>
+      <c r="C106" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="F106" s="8"/>
     </row>
     <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7422,7 +7597,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>25.9</v>
+        <v>27.4</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>13</v>
@@ -7434,7 +7609,7 @@
       </c>
       <c r="B5" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="18">
         <v>90</v>
@@ -7446,7 +7621,7 @@
       </c>
       <c r="B6" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>11.9</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7471,7 +7646,7 @@
       </c>
       <c r="F8" s="19">
         <f>SUM(Tableau13[Temps '[h']])</f>
-        <v>53.3</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7480,7 +7655,7 @@
       </c>
       <c r="B9" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7495,7 +7670,7 @@
       <c r="B11" s="11"/>
       <c r="F11" s="19">
         <f>F8-F5</f>
-        <v>-36.700000000000003</v>
+        <v>-27.450000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/docs/TPI_Journal_de_Travail_Anthony.xlsx
+++ b/docs/TPI_Journal_de_Travail_Anthony.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/pv22nbo_eduvaud_ch/Documents/Bureau/TPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2131" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4649454-165F-4FE0-B30F-EA36E5D9EB9C}"/>
+  <xr:revisionPtr revIDLastSave="2260" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C5A0C61-528D-4A6A-AF67-C42B51733E11}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$F$106</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$F$119</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="183">
   <si>
     <t>Jour</t>
   </si>
@@ -538,6 +538,60 @@
   </si>
   <si>
     <t xml:space="preserve">Test Fonctionnels </t>
+  </si>
+  <si>
+    <t>Voir Mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amélioration du code pour les commentaires et Docstring </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amélioration Login.py  </t>
+  </si>
+  <si>
+    <t>Finalisation de la Partie 3 Réalisation</t>
+  </si>
+  <si>
+    <t>Gestion d'erreur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de l'en tête pour le fichier test </t>
+  </si>
+  <si>
+    <t xml:space="preserve">README </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout du port </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification du fichier .env + modifier dans le code </t>
+  </si>
+  <si>
+    <t>Mis a jour de l'image de l'architecture de l'application + Partie 3.2.3</t>
+  </si>
+  <si>
+    <t>La date de naissance est modifiable alors qu'elle ne doit pas l'être</t>
+  </si>
+  <si>
+    <t>Changement date de naissance dans Gestion des entité</t>
+  </si>
+  <si>
+    <t>Partie Conclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Documentation </t>
+  </si>
+  <si>
+    <t>Voir si d'autres erreur restantes ou problème</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test complet de l'application </t>
+  </si>
+  <si>
+    <t>Pour le Numéro de téléphone , Pas fini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Régler Problème CRUD Parents  </t>
   </si>
 </sst>
 </file>
@@ -1284,22 +1338,22 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27.4</c:v>
+                  <c:v>30.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.399999999999999</c:v>
+                  <c:v>19.149999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.25</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1971,7 +2025,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9300253" cy="6057472"/>
+    <xdr:ext cx="9290911" cy="6045953"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1">
@@ -4370,107 +4424,255 @@
       <c r="F106" s="8"/>
     </row>
     <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="14"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="7"/>
+      <c r="A107" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B107" s="14">
+        <v>4</v>
+      </c>
+      <c r="C107" s="11">
+        <v>1</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
+      <c r="F107" s="8" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="108" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="6"/>
-      <c r="B108" s="14"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="8"/>
+      <c r="A108" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B108" s="14">
+        <v>4</v>
+      </c>
+      <c r="C108" s="11">
+        <v>1</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="F108" s="8"/>
     </row>
     <row r="109" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="14"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
+      <c r="A109" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B109" s="14">
+        <v>4</v>
+      </c>
+      <c r="C109" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="110" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6"/>
-      <c r="B110" s="14"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
+      <c r="A110" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B110" s="14">
+        <v>4</v>
+      </c>
+      <c r="C110" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="111" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="14"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="8"/>
+      <c r="A111" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B111" s="14">
+        <v>4</v>
+      </c>
+      <c r="C111" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="F111" s="8"/>
     </row>
     <row r="112" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="14"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
+      <c r="A112" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B112" s="14">
+        <v>4</v>
+      </c>
+      <c r="C112" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="113" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="14"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
+      <c r="A113" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B113" s="14">
+        <v>4</v>
+      </c>
+      <c r="C113" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="114" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6"/>
-      <c r="B114" s="14"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
+      <c r="A114" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B114" s="14">
+        <v>4</v>
+      </c>
+      <c r="C114" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="115" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="6"/>
-      <c r="B115" s="14"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
+      <c r="A115" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B115" s="14">
+        <v>4</v>
+      </c>
+      <c r="C115" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="116" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="6"/>
-      <c r="B116" s="14"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
+      <c r="A116" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B116" s="14">
+        <v>4</v>
+      </c>
+      <c r="C116" s="11">
+        <v>1.75</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="117" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="14"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
+      <c r="A117" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B117" s="14">
+        <v>4</v>
+      </c>
+      <c r="C117" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="118" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="6"/>
-      <c r="B118" s="14"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
+      <c r="A118" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B118" s="14">
+        <v>4</v>
+      </c>
+      <c r="C118" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="119" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="6"/>
-      <c r="B119" s="14"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="8"/>
+      <c r="A119" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B119" s="14">
+        <v>4</v>
+      </c>
+      <c r="C119" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="F119" s="8"/>
     </row>
     <row r="120" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7534,6 +7736,9 @@
   </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="101" max="5" man="1"/>
+  </rowBreaks>
   <ignoredErrors>
     <ignoredError sqref="B1:D1" listDataValidation="1"/>
   </ignoredErrors>
@@ -7597,7 +7802,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>27.4</v>
+        <v>30.9</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>13</v>
@@ -7609,7 +7814,7 @@
       </c>
       <c r="B5" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F5" s="18">
         <v>90</v>
@@ -7621,7 +7826,7 @@
       </c>
       <c r="B6" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>16.399999999999999</v>
+        <v>19.149999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7642,11 +7847,11 @@
       </c>
       <c r="B8" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="19">
         <f>SUM(Tableau13[Temps '[h']])</f>
-        <v>62.55</v>
+        <v>70.55</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7655,7 +7860,7 @@
       </c>
       <c r="B9" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7670,7 +7875,7 @@
       <c r="B11" s="11"/>
       <c r="F11" s="19">
         <f>F8-F5</f>
-        <v>-27.450000000000003</v>
+        <v>-19.450000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
